--- a/ad_stats_log.xlsx
+++ b/ad_stats_log.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C232"/>
+  <dimension ref="A1:C241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -4162,6 +4162,159 @@
         </is>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2025-05-06 09:35:45</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Young Adult (20-34)</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2025-05-06 09:54:50</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Middle-aged Adult (35-49)</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2025-05-06 09:55:38</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Young Adult (20-34)</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2025-05-07 12:37:50</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Young Adult (20-34)</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Woman</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2025-05-07 12:41:53</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Young Adult (20-34)</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2025-06-02 20:29:31</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Young Adult (20-34)</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2025-06-02 20:29:32</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Young Adult (20-34)</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2025-06-02 20:29:32</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Young Adult (20-34)</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2025-06-02 20:29:32</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Middle-aged Adult (35-49)</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
